--- a/data/trans_orig/P25C$parches_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según método de dejar de fumar (multirrespuesta) en 2023</t>
+          <t>Población según método de dejar de fumar (multirrespuesta) en 2023 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>7070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99941</t>
+          <t>99768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115582</t>
+          <t>115455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51008</t>
+          <t>51392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60202</t>
+          <t>60221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154846</t>
+          <t>155097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173911</t>
+          <t>173157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>20419</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>7379</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>840</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>5767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79313</t>
+          <t>79045</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89751</t>
+          <t>89629</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47949</t>
+          <t>48777</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54734</t>
+          <t>54830</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130466</t>
+          <t>130610</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142736</t>
+          <t>142462</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5541</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>304372</t>
+          <t>304136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>338542</t>
+          <t>338365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17224</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324356</t>
+          <t>324519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>360869</t>
+          <t>359646</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17176</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19105</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7679</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>730</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>541</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>158583</t>
+          <t>158549</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>175408</t>
+          <t>175416</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>66366</t>
+          <t>65757</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>74877</t>
+          <t>74683</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229415</t>
+          <t>229215</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>248126</t>
+          <t>248299</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>15834</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>9580</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>570</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3126</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>71408</t>
+          <t>70709</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>82919</t>
+          <t>82957</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>55469</t>
+          <t>55509</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>64221</t>
+          <t>64486</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>129858</t>
+          <t>129633</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>145281</t>
+          <t>144523</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>430</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>449</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33350</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>37332</t>
+          <t>37139</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>17642</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>14606</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>27754</t>
+          <t>27640</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,82 +5741,82 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2304</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>7794</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
           <t>0,05%</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>1946</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>2708</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="T48" s="2" t="inlineStr">
-        <is>
-          <t>8184</t>
-        </is>
-      </c>
-      <c r="U48" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>743272</t>
+          <t>744622</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>811680</t>
+          <t>815747</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>286226</t>
+          <t>287663</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>304251</t>
+          <t>304498</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1041484</t>
+          <t>1040795</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1123271</t>
+          <t>1121588</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>39508</t>
+          <t>40431</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>15611</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>47317</t>
+          <t>47807</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -6178,12 +6178,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>40750</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>48418</t>
+          <t>50284</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P25C$parches_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P25C$parches_2023-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>696</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2515</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2386</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>389</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6771</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>109043</t>
+          <t>115260</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99768</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115455</t>
+          <t>122204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>56582</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51392</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60221</t>
+          <t>64203</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>165624</t>
+          <t>175960</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155097</t>
+          <t>164074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>173157</t>
+          <t>183914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>10181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>24050</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>681</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>710</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>710</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>3580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85489</t>
+          <t>93443</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>79045</t>
+          <t>87016</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>98467</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52413</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48777</t>
+          <t>53028</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54830</t>
+          <t>60357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>137901</t>
+          <t>151069</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130610</t>
+          <t>143046</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142462</t>
+          <t>157027</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>437</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8484</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8829</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>797</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>665</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>330904</t>
+          <t>95335</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>304136</t>
+          <t>88237</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>338365</t>
+          <t>100127</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>17692</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>350968</t>
+          <t>116141</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324519</t>
+          <t>109173</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>359646</t>
+          <t>121423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -2880,67 +2880,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>4261</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1123</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4068</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1761</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2993,67 +2993,67 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2171</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4181</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>3266</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -3110,59 +3110,59 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4277</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>553</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>11719</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>168621</t>
+          <t>187819</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>158549</t>
+          <t>176725</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>175416</t>
+          <t>196136</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>71141</t>
+          <t>76595</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>65757</t>
+          <t>71166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>74683</t>
+          <t>80405</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>239763</t>
+          <t>264414</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>229215</t>
+          <t>252511</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>248299</t>
+          <t>273021</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7772</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16553</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>8418</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>566</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2199</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9580</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>571</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>667</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>667</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>78110</t>
+          <t>83808</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>70709</t>
+          <t>75956</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>82957</t>
+          <t>88458</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>60356</t>
+          <t>69628</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>55509</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>64486</t>
+          <t>73811</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>138466</t>
+          <t>153436</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>129633</t>
+          <t>144607</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>144523</t>
+          <t>160013</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>435</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -4583,32 +4583,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,39 +4653,39 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>498</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -4745,12 +4745,12 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>491</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5233</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5187,27 +5187,27 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>34129</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>41563</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>37139</t>
+          <t>37875</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>14606</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>9250</t>
+          <t>13261</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>27640</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>10382</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>3869</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>16702</t>
+          <t>17634</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -5721,67 +5721,67 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2279</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>17782</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>777628</t>
+          <t>580899</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>744622</t>
+          <t>563490</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>815747</t>
+          <t>594593</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>296659</t>
+          <t>322348</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>287663</t>
+          <t>313049</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>304498</t>
+          <t>331014</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1074286</t>
+          <t>903245</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1040795</t>
+          <t>883937</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1121588</t>
+          <t>920037</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>37400</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9807</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>47807</t>
+          <t>49630</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6173,32 +6173,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>24296</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>18704</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>39461</t>
+          <t>41156</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>16190</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>33763</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>16077</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>50284</t>
+          <t>51368</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
